--- a/test_data/my_hand.xlsx
+++ b/test_data/my_hand.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="14055" firstSheet="10" activeTab="13"/>
+    <workbookView windowWidth="27945" windowHeight="14055" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="get_gripper_firmware_version" sheetId="1" r:id="rId1"/>
@@ -4308,7 +4308,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6097,7 +6097,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>14</v>
@@ -6117,7 +6117,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>14</v>
@@ -6137,7 +6137,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>14</v>
@@ -6157,7 +6157,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>14</v>
@@ -6177,7 +6177,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>14</v>
@@ -6197,7 +6197,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>14</v>
